--- a/eval/results/evaluation_metrics.xlsx
+++ b/eval/results/evaluation_metrics.xlsx
@@ -520,19 +520,19 @@
         <v>1920</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9197916666666667</v>
+        <v>0.9208333333333333</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9319444444444445</v>
+        <v>0.9321329639889196</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8646907216494846</v>
+        <v>0.8672680412371134</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8970588235294118</v>
+        <v>0.8985313751668893</v>
       </c>
       <c r="F3" t="n">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="G3" t="n">
         <v>1095</v>
@@ -541,7 +541,7 @@
         <v>49</v>
       </c>
       <c r="I3" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -554,19 +554,19 @@
         <v>1920</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8604166666666667</v>
+        <v>0.8598958333333333</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8290155440414507</v>
+        <v>0.8287937743190662</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8247422680412371</v>
+        <v>0.8234536082474226</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8268733850129197</v>
+        <v>0.8261150614091791</v>
       </c>
       <c r="F4" t="n">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="G4" t="n">
         <v>1012</v>
@@ -575,7 +575,7 @@
         <v>132</v>
       </c>
       <c r="I4" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -588,19 +588,19 @@
         <v>1920</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7927083333333333</v>
+        <v>0.79375</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7547169811320755</v>
+        <v>0.7553763440860215</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7216494845360825</v>
+        <v>0.7242268041237113</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7378129117259553</v>
+        <v>0.7394736842105263</v>
       </c>
       <c r="F5" t="n">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="G5" t="n">
         <v>962</v>
@@ -609,7 +609,7 @@
         <v>182</v>
       </c>
       <c r="I5" t="n">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         <v>1920</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8708333333333333</v>
+        <v>0.8713541666666667</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9599303135888502</v>
+        <v>0.96</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7100515463917526</v>
+        <v>0.711340206185567</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8162962962962963</v>
+        <v>0.8171724648408586</v>
       </c>
       <c r="F6" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="G6" t="n">
         <v>1121</v>
@@ -643,7 +643,7 @@
         <v>23</v>
       </c>
       <c r="I6" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -758,19 +758,19 @@
         <v>1920</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.7682291666666666</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6771058315334774</v>
+        <v>0.6781485468245425</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8079896907216495</v>
+        <v>0.8118556701030928</v>
       </c>
       <c r="E10" t="n">
-        <v>0.736780258519389</v>
+        <v>0.7390029325513195</v>
       </c>
       <c r="F10" t="n">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="G10" t="n">
         <v>845</v>
@@ -779,7 +779,7 @@
         <v>299</v>
       </c>
       <c r="I10" t="n">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -892,19 +892,19 @@
         <v>1920</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9197916666666667</v>
+        <v>0.9208333333333333</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9319444444444445</v>
+        <v>0.9321329639889196</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8646907216494846</v>
+        <v>0.8672680412371134</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8970588235294118</v>
+        <v>0.8985313751668893</v>
       </c>
       <c r="F3" t="n">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="G3" t="n">
         <v>1095</v>
@@ -913,7 +913,7 @@
         <v>49</v>
       </c>
       <c r="I3" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -926,19 +926,19 @@
         <v>1920</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8604166666666667</v>
+        <v>0.8598958333333333</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8290155440414507</v>
+        <v>0.8287937743190662</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8247422680412371</v>
+        <v>0.8234536082474226</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8268733850129197</v>
+        <v>0.8261150614091791</v>
       </c>
       <c r="F4" t="n">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="G4" t="n">
         <v>1012</v>
@@ -947,7 +947,7 @@
         <v>132</v>
       </c>
       <c r="I4" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -960,19 +960,19 @@
         <v>1920</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7927083333333333</v>
+        <v>0.79375</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7547169811320755</v>
+        <v>0.7553763440860215</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7216494845360825</v>
+        <v>0.7242268041237113</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7378129117259553</v>
+        <v>0.7394736842105263</v>
       </c>
       <c r="F5" t="n">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="G5" t="n">
         <v>962</v>
@@ -981,7 +981,7 @@
         <v>182</v>
       </c>
       <c r="I5" t="n">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -994,19 +994,19 @@
         <v>1920</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8708333333333333</v>
+        <v>0.8713541666666667</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9599303135888502</v>
+        <v>0.96</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7100515463917526</v>
+        <v>0.711340206185567</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8162962962962963</v>
+        <v>0.8171724648408586</v>
       </c>
       <c r="F6" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="G6" t="n">
         <v>1121</v>
@@ -1015,7 +1015,7 @@
         <v>23</v>
       </c>
       <c r="I6" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1130,19 +1130,19 @@
         <v>1920</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.7682291666666666</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6771058315334774</v>
+        <v>0.6781485468245425</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8079896907216495</v>
+        <v>0.8118556701030928</v>
       </c>
       <c r="E10" t="n">
-        <v>0.736780258519389</v>
+        <v>0.7390029325513195</v>
       </c>
       <c r="F10" t="n">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="G10" t="n">
         <v>845</v>
@@ -1151,7 +1151,7 @@
         <v>299</v>
       </c>
       <c r="I10" t="n">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>

--- a/eval/results/evaluation_metrics.xlsx
+++ b/eval/results/evaluation_metrics.xlsx
@@ -520,19 +520,19 @@
         <v>1920</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9208333333333333</v>
+        <v>0.9213541666666667</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9321329639889196</v>
+        <v>0.9322268326417704</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8672680412371134</v>
+        <v>0.8685567010309279</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8985313751668893</v>
+        <v>0.8992661774516344</v>
       </c>
       <c r="F3" t="n">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="G3" t="n">
         <v>1095</v>
@@ -541,7 +541,7 @@
         <v>49</v>
       </c>
       <c r="I3" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -588,19 +588,19 @@
         <v>1920</v>
       </c>
       <c r="B5" t="n">
-        <v>0.79375</v>
+        <v>0.7942708333333334</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7553763440860215</v>
+        <v>0.7557046979865771</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7242268041237113</v>
+        <v>0.7255154639175257</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7394736842105263</v>
+        <v>0.7403024326101247</v>
       </c>
       <c r="F5" t="n">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="G5" t="n">
         <v>962</v>
@@ -609,7 +609,7 @@
         <v>182</v>
       </c>
       <c r="I5" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -656,19 +656,19 @@
         <v>1920</v>
       </c>
       <c r="B7" t="n">
-        <v>0.8802083333333334</v>
+        <v>0.8807291666666667</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8719346049046321</v>
+        <v>0.8721088435374149</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8247422680412371</v>
+        <v>0.8260309278350515</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8476821192052979</v>
+        <v>0.8484447385837194</v>
       </c>
       <c r="F7" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="G7" t="n">
         <v>1050</v>
@@ -677,7 +677,7 @@
         <v>94</v>
       </c>
       <c r="I7" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -690,19 +690,19 @@
         <v>1920</v>
       </c>
       <c r="B8" t="n">
-        <v>0.7979166666666667</v>
+        <v>0.7984375</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7957317073170732</v>
+        <v>0.7960426179604262</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6726804123711341</v>
+        <v>0.6739690721649485</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7290502793296091</v>
+        <v>0.7299371946964411</v>
       </c>
       <c r="F8" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G8" t="n">
         <v>1010</v>
@@ -711,7 +711,7 @@
         <v>134</v>
       </c>
       <c r="I8" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -892,19 +892,19 @@
         <v>1920</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9208333333333333</v>
+        <v>0.9213541666666667</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9321329639889196</v>
+        <v>0.9322268326417704</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8672680412371134</v>
+        <v>0.8685567010309279</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8985313751668893</v>
+        <v>0.8992661774516344</v>
       </c>
       <c r="F3" t="n">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="G3" t="n">
         <v>1095</v>
@@ -913,7 +913,7 @@
         <v>49</v>
       </c>
       <c r="I3" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -960,19 +960,19 @@
         <v>1920</v>
       </c>
       <c r="B5" t="n">
-        <v>0.79375</v>
+        <v>0.7942708333333334</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7553763440860215</v>
+        <v>0.7557046979865771</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7242268041237113</v>
+        <v>0.7255154639175257</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7394736842105263</v>
+        <v>0.7403024326101247</v>
       </c>
       <c r="F5" t="n">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="G5" t="n">
         <v>962</v>
@@ -981,7 +981,7 @@
         <v>182</v>
       </c>
       <c r="I5" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -1028,19 +1028,19 @@
         <v>1920</v>
       </c>
       <c r="B7" t="n">
-        <v>0.8802083333333334</v>
+        <v>0.8807291666666667</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8719346049046321</v>
+        <v>0.8721088435374149</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8247422680412371</v>
+        <v>0.8260309278350515</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8476821192052979</v>
+        <v>0.8484447385837194</v>
       </c>
       <c r="F7" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="G7" t="n">
         <v>1050</v>
@@ -1049,7 +1049,7 @@
         <v>94</v>
       </c>
       <c r="I7" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1062,19 +1062,19 @@
         <v>1920</v>
       </c>
       <c r="B8" t="n">
-        <v>0.7979166666666667</v>
+        <v>0.7984375</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7957317073170732</v>
+        <v>0.7960426179604262</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6726804123711341</v>
+        <v>0.6739690721649485</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7290502793296091</v>
+        <v>0.7299371946964411</v>
       </c>
       <c r="F8" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G8" t="n">
         <v>1010</v>
@@ -1083,7 +1083,7 @@
         <v>134</v>
       </c>
       <c r="I8" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>

--- a/eval/results/evaluation_metrics.xlsx
+++ b/eval/results/evaluation_metrics.xlsx
@@ -483,31 +483,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1920</v>
+        <v>2400</v>
       </c>
       <c r="B2" t="n">
-        <v>0.84375</v>
+        <v>0.8220833333333334</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8814102564102564</v>
+        <v>0.8397790055248618</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7087628865979382</v>
+        <v>0.7293666026871402</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.7806882383153571</v>
       </c>
       <c r="F2" t="n">
-        <v>550</v>
+        <v>760</v>
       </c>
       <c r="G2" t="n">
-        <v>1070</v>
+        <v>1213</v>
       </c>
       <c r="H2" t="n">
-        <v>74</v>
+        <v>145</v>
       </c>
       <c r="I2" t="n">
-        <v>226</v>
+        <v>282</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -517,31 +517,31 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1920</v>
+        <v>2400</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9213541666666667</v>
+        <v>0.89125</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9322268326417704</v>
+        <v>0.90216271884655</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8685567010309279</v>
+        <v>0.8406909788867563</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8992661774516344</v>
+        <v>0.8703427719821163</v>
       </c>
       <c r="F3" t="n">
-        <v>674</v>
+        <v>876</v>
       </c>
       <c r="G3" t="n">
-        <v>1095</v>
+        <v>1263</v>
       </c>
       <c r="H3" t="n">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="I3" t="n">
-        <v>102</v>
+        <v>166</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -551,31 +551,31 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1920</v>
+        <v>2400</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8598958333333333</v>
+        <v>0.8429166666666666</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8287937743190662</v>
+        <v>0.8348439073514602</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8234536082474226</v>
+        <v>0.7955854126679462</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8261150614091791</v>
+        <v>0.8147420147420148</v>
       </c>
       <c r="F4" t="n">
-        <v>639</v>
+        <v>829</v>
       </c>
       <c r="G4" t="n">
-        <v>1012</v>
+        <v>1194</v>
       </c>
       <c r="H4" t="n">
-        <v>132</v>
+        <v>164</v>
       </c>
       <c r="I4" t="n">
-        <v>137</v>
+        <v>213</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -585,31 +585,31 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1920</v>
+        <v>2400</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7942708333333334</v>
+        <v>0.7945833333333333</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7557046979865771</v>
+        <v>0.7747747747747747</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7255154639175257</v>
+        <v>0.7428023032629558</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7403024326101247</v>
+        <v>0.758451739343459</v>
       </c>
       <c r="F5" t="n">
-        <v>563</v>
+        <v>774</v>
       </c>
       <c r="G5" t="n">
-        <v>962</v>
+        <v>1133</v>
       </c>
       <c r="H5" t="n">
-        <v>182</v>
+        <v>225</v>
       </c>
       <c r="I5" t="n">
-        <v>213</v>
+        <v>268</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -619,31 +619,31 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1920</v>
+        <v>2400</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8713541666666667</v>
+        <v>0.8470833333333333</v>
       </c>
       <c r="C6" t="n">
-        <v>0.96</v>
+        <v>0.9343629343629344</v>
       </c>
       <c r="D6" t="n">
-        <v>0.711340206185567</v>
+        <v>0.6967370441458733</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8171724648408586</v>
+        <v>0.7982407916437604</v>
       </c>
       <c r="F6" t="n">
-        <v>552</v>
+        <v>726</v>
       </c>
       <c r="G6" t="n">
-        <v>1121</v>
+        <v>1307</v>
       </c>
       <c r="H6" t="n">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="I6" t="n">
-        <v>224</v>
+        <v>316</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -653,31 +653,31 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1920</v>
+        <v>2400</v>
       </c>
       <c r="B7" t="n">
-        <v>0.8807291666666667</v>
+        <v>0.8683333333333333</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8721088435374149</v>
+        <v>0.8773388773388774</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8260309278350515</v>
+        <v>0.8099808061420346</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8484447385837194</v>
+        <v>0.8423153692614772</v>
       </c>
       <c r="F7" t="n">
-        <v>641</v>
+        <v>844</v>
       </c>
       <c r="G7" t="n">
-        <v>1050</v>
+        <v>1240</v>
       </c>
       <c r="H7" t="n">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="I7" t="n">
-        <v>135</v>
+        <v>198</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -687,31 +687,31 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1920</v>
+        <v>2400</v>
       </c>
       <c r="B8" t="n">
-        <v>0.7984375</v>
+        <v>0.7758333333333334</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7960426179604262</v>
+        <v>0.794392523364486</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6739690721649485</v>
+        <v>0.6525911708253359</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7299371946964411</v>
+        <v>0.7165437302423603</v>
       </c>
       <c r="F8" t="n">
-        <v>523</v>
+        <v>680</v>
       </c>
       <c r="G8" t="n">
-        <v>1010</v>
+        <v>1182</v>
       </c>
       <c r="H8" t="n">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="I8" t="n">
-        <v>253</v>
+        <v>362</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -721,31 +721,31 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1920</v>
+        <v>2400</v>
       </c>
       <c r="B9" t="n">
-        <v>0.8135416666666667</v>
+        <v>0.7841666666666667</v>
       </c>
       <c r="C9" t="n">
-        <v>0.898854961832061</v>
+        <v>0.8797101449275362</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6069587628865979</v>
+        <v>0.5825335892514395</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7246153846153846</v>
+        <v>0.7009237875288683</v>
       </c>
       <c r="F9" t="n">
-        <v>471</v>
+        <v>607</v>
       </c>
       <c r="G9" t="n">
-        <v>1091</v>
+        <v>1275</v>
       </c>
       <c r="H9" t="n">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="I9" t="n">
-        <v>305</v>
+        <v>435</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -755,31 +755,31 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1920</v>
+        <v>2400</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7682291666666666</v>
+        <v>0.7795833333333333</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6781485468245425</v>
+        <v>0.7107641741988496</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8118556701030928</v>
+        <v>0.8301343570057581</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7390029325513195</v>
+        <v>0.7658255865427179</v>
       </c>
       <c r="F10" t="n">
-        <v>630</v>
+        <v>865</v>
       </c>
       <c r="G10" t="n">
-        <v>845</v>
+        <v>1006</v>
       </c>
       <c r="H10" t="n">
-        <v>299</v>
+        <v>352</v>
       </c>
       <c r="I10" t="n">
-        <v>146</v>
+        <v>177</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -855,31 +855,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1920</v>
+        <v>2400</v>
       </c>
       <c r="B2" t="n">
-        <v>0.84375</v>
+        <v>0.8220833333333334</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8814102564102564</v>
+        <v>0.8397790055248618</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7087628865979382</v>
+        <v>0.7293666026871402</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.7806882383153571</v>
       </c>
       <c r="F2" t="n">
-        <v>550</v>
+        <v>760</v>
       </c>
       <c r="G2" t="n">
-        <v>1070</v>
+        <v>1213</v>
       </c>
       <c r="H2" t="n">
-        <v>74</v>
+        <v>145</v>
       </c>
       <c r="I2" t="n">
-        <v>226</v>
+        <v>282</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -889,31 +889,31 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1920</v>
+        <v>2400</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9213541666666667</v>
+        <v>0.89125</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9322268326417704</v>
+        <v>0.90216271884655</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8685567010309279</v>
+        <v>0.8406909788867563</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8992661774516344</v>
+        <v>0.8703427719821163</v>
       </c>
       <c r="F3" t="n">
-        <v>674</v>
+        <v>876</v>
       </c>
       <c r="G3" t="n">
-        <v>1095</v>
+        <v>1263</v>
       </c>
       <c r="H3" t="n">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="I3" t="n">
-        <v>102</v>
+        <v>166</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -923,31 +923,31 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1920</v>
+        <v>2400</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8598958333333333</v>
+        <v>0.8429166666666666</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8287937743190662</v>
+        <v>0.8348439073514602</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8234536082474226</v>
+        <v>0.7955854126679462</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8261150614091791</v>
+        <v>0.8147420147420148</v>
       </c>
       <c r="F4" t="n">
-        <v>639</v>
+        <v>829</v>
       </c>
       <c r="G4" t="n">
-        <v>1012</v>
+        <v>1194</v>
       </c>
       <c r="H4" t="n">
-        <v>132</v>
+        <v>164</v>
       </c>
       <c r="I4" t="n">
-        <v>137</v>
+        <v>213</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -957,31 +957,31 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1920</v>
+        <v>2400</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7942708333333334</v>
+        <v>0.7945833333333333</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7557046979865771</v>
+        <v>0.7747747747747747</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7255154639175257</v>
+        <v>0.7428023032629558</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7403024326101247</v>
+        <v>0.758451739343459</v>
       </c>
       <c r="F5" t="n">
-        <v>563</v>
+        <v>774</v>
       </c>
       <c r="G5" t="n">
-        <v>962</v>
+        <v>1133</v>
       </c>
       <c r="H5" t="n">
-        <v>182</v>
+        <v>225</v>
       </c>
       <c r="I5" t="n">
-        <v>213</v>
+        <v>268</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -991,31 +991,31 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1920</v>
+        <v>2400</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8713541666666667</v>
+        <v>0.8470833333333333</v>
       </c>
       <c r="C6" t="n">
-        <v>0.96</v>
+        <v>0.9343629343629344</v>
       </c>
       <c r="D6" t="n">
-        <v>0.711340206185567</v>
+        <v>0.6967370441458733</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8171724648408586</v>
+        <v>0.7982407916437604</v>
       </c>
       <c r="F6" t="n">
-        <v>552</v>
+        <v>726</v>
       </c>
       <c r="G6" t="n">
-        <v>1121</v>
+        <v>1307</v>
       </c>
       <c r="H6" t="n">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="I6" t="n">
-        <v>224</v>
+        <v>316</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1025,31 +1025,31 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1920</v>
+        <v>2400</v>
       </c>
       <c r="B7" t="n">
-        <v>0.8807291666666667</v>
+        <v>0.8683333333333333</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8721088435374149</v>
+        <v>0.8773388773388774</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8260309278350515</v>
+        <v>0.8099808061420346</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8484447385837194</v>
+        <v>0.8423153692614772</v>
       </c>
       <c r="F7" t="n">
-        <v>641</v>
+        <v>844</v>
       </c>
       <c r="G7" t="n">
-        <v>1050</v>
+        <v>1240</v>
       </c>
       <c r="H7" t="n">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="I7" t="n">
-        <v>135</v>
+        <v>198</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1059,31 +1059,31 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1920</v>
+        <v>2400</v>
       </c>
       <c r="B8" t="n">
-        <v>0.7984375</v>
+        <v>0.7758333333333334</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7960426179604262</v>
+        <v>0.794392523364486</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6739690721649485</v>
+        <v>0.6525911708253359</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7299371946964411</v>
+        <v>0.7165437302423603</v>
       </c>
       <c r="F8" t="n">
-        <v>523</v>
+        <v>680</v>
       </c>
       <c r="G8" t="n">
-        <v>1010</v>
+        <v>1182</v>
       </c>
       <c r="H8" t="n">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="I8" t="n">
-        <v>253</v>
+        <v>362</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1093,31 +1093,31 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1920</v>
+        <v>2400</v>
       </c>
       <c r="B9" t="n">
-        <v>0.8135416666666667</v>
+        <v>0.7841666666666667</v>
       </c>
       <c r="C9" t="n">
-        <v>0.898854961832061</v>
+        <v>0.8797101449275362</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6069587628865979</v>
+        <v>0.5825335892514395</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7246153846153846</v>
+        <v>0.7009237875288683</v>
       </c>
       <c r="F9" t="n">
-        <v>471</v>
+        <v>607</v>
       </c>
       <c r="G9" t="n">
-        <v>1091</v>
+        <v>1275</v>
       </c>
       <c r="H9" t="n">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="I9" t="n">
-        <v>305</v>
+        <v>435</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1127,31 +1127,31 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1920</v>
+        <v>2400</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7682291666666666</v>
+        <v>0.7795833333333333</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6781485468245425</v>
+        <v>0.7107641741988496</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8118556701030928</v>
+        <v>0.8301343570057581</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7390029325513195</v>
+        <v>0.7658255865427179</v>
       </c>
       <c r="F10" t="n">
-        <v>630</v>
+        <v>865</v>
       </c>
       <c r="G10" t="n">
-        <v>845</v>
+        <v>1006</v>
       </c>
       <c r="H10" t="n">
-        <v>299</v>
+        <v>352</v>
       </c>
       <c r="I10" t="n">
-        <v>146</v>
+        <v>177</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
